--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0041.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0041.xlsx
@@ -1289,7 +1289,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Lần đầu ta thấy hắn như vậy. Theo dõi xem hắn đi đâu nào.</t>
+          <t>Lần đầu tao thấy hắn như vậy. Theo dõi xem hắn đi đâu nào.</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Ôi, {Male=anh;Female=chị} {PlayerName}, {Male=anh;Female=chị} đến rồi! Nhờ có {Male=anh;Female=chị}, phần lớn sức mạnh của bức tranh đã được khôi phục. Và nhìn kìa, một người bạn mới đã gia nhập ngôi làng nhỏ của chúng ta!</t>
+          <t>Ôi, {Male=Mr.;Female=Ms.} {PlayerName}, bạn đến rồi! Nhờ có bạn, phần lớn sức mạnh của bức tranh đã được khôi phục. Và nhìn kìa, một người bạn mới đã gia nhập ngôi làng nhỏ của chúng ta!</t>
         </is>
       </c>
     </row>
@@ -2524,7 +2524,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Ngươi, {Male=ngài;Female=nữ sĩ} {PlayerName}, mới chính là anh hùng thực sự!</t>
+          <t>Ngươi, {Male=Mr.;Female=Ms.} {PlayerName}, mới chính là anh hùng thực sự!</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Ha, {PlayerName} nhà triết học à... nhưng câu hỏi này thì quá sâu với ta rồi.</t>
+          <t>Ha, {PlayerName} nhà triết học à... nhưng câu hỏi này thì quá sâu với tao rồi.</t>
         </is>
       </c>
     </row>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>{Male=Anh;Female=Chị} {PlayerName}, {Male=anh;Female=chị} có rảnh không?</t>
+          <t>{Male=Mr.;Female=Ms.} {PlayerName}, bạn có rảnh không?</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>À, {Male=anh;Female=chị} {PlayerName}, cậu đến rồi à.</t>
+          <t>À, {Male=Mr.;Female=Ms.} {PlayerName}, cậu đến rồi à.</t>
         </is>
       </c>
     </row>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Cậu thấy đấy, một số Tiếng Vang vẫn đang hoạt động kỳ lạ, dù ta đã khôi phục bức tranh về trạng thái đầy đủ sức mạnh. Tôi đang yêu cầu trụ sở gửi thêm điều tra viên thực địa để giải quyết chuyện này.</t>
+          <t>Cậu thấy đấy, một số Echo vẫn đang hoạt động kỳ lạ, dù ta đã khôi phục bức tranh về trạng thái đầy đủ sức mạnh. Tôi đang yêu cầu trụ sở gửi thêm điều tra viên thực địa để giải quyết chuyện này.</t>
         </is>
       </c>
     </row>
@@ -4474,7 +4474,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>À, nhân tiện, tớ có thứ này muốn tặng cậu, {Male=anh;Female=chị} {PlayerName}.</t>
+          <t>À, nhân tiện, tớ có thứ này muốn tặng cậu, {Male=Mr.;Female=Ms.} {PlayerName}.</t>
         </is>
       </c>
     </row>
@@ -5514,7 +5514,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>{Male=Anh;Female=Chị} {PlayerName}, {Male=anh;Female=chị} đang ở Làng Gấu Bông à?</t>
+          <t>{Male=Mr.;Female=Ms.} {PlayerName}, bạn đang ở Làng Gấu Bông à?</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>{Male=Anh;Female=Chị} {PlayerName}, {Male=anh;Female=chị} có thể giúp tôi đến Thị trấn Egla &lt;color=yellow&gt;during the day&lt;/color&gt; và tìm hiểu xem tại sao ông Bake lại rời tiệm bánh không?</t>
+          <t>{Male=Mr.;Female=Ms.} {PlayerName}, bạn có thể giúp tôi đến Thị trấn Egla &lt;color=yellow&gt;vào ban ngày&lt;/color&gt; và tìm hiểu xem tại sao ông Bake lại rời tiệm bánh không?</t>
         </is>
       </c>
     </row>
@@ -6879,7 +6879,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>{Male=Anh;Female=Chị} {PlayerName}! Cậu đến đúng lúc đấy! Nhìn đằng kia kìa!</t>
+          <t>{Male=Mr.;Female=Ms.} {PlayerName}! Cậu đến đúng lúc đấy! Nhìn đằng kia kìa!</t>
         </is>
       </c>
     </row>
@@ -7334,7 +7334,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Tất cả là nhờ cậu. Đời này ta chắc chẳng bao giờ tìm được nhiều Rương như vậy đâu.</t>
+          <t>Tất cả là nhờ cậu. Đời này tao chắc chẳng bao giờ tìm được nhiều Rương như vậy đâu.</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Nhắc đến chuyện này, Quả Cầu Sonoro trong bức tranh nhỏ hơn nhiều so với kích thước tiềm năng đã ghi nhận, nghĩa là vẫn còn nhiều phần thưởng chờ được nhận!</t>
+          <t>Nhắc đến chuyện này, Sonoro Sphere trong bức tranh nhỏ hơn nhiều so với kích thước tiềm năng đã ghi nhận, nghĩa là vẫn còn nhiều phần thưởng chờ được nhận!</t>
         </is>
       </c>
     </row>
@@ -8504,7 +8504,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>{Male=Anh;Female=Chị} {PlayerName}, làm ơn giúp tôi thuyết phục những người Gondola rời đi! Chúng tôi, những Tín Đồ, không được phép quá gần gũi với Echoes!</t>
+          <t>{Male=Mr.;Female=Ms.} {PlayerName}, làm ơn giúp tôi thuyết phục những người Gondola rời đi! Chúng tôi, những Tín Đồ, không được phép quá gần gũi với Echoes!</t>
         </is>
       </c>
     </row>
@@ -9349,7 +9349,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>{Male=Anh;Female=Chị} {PlayerName}, lần này để tôi đi cùng {Male=anh;Female=chị} nhé!</t>
+          <t>{Male=Mr.;Female=Ms.} {PlayerName}, lần này để tôi đi cùng bạn nhé!</t>
         </is>
       </c>
     </row>
@@ -9544,7 +9544,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Đi theo ta nhé, {Male=anh;Female=chị} {PlayerName}—chúng ta cần một chiếc Gondola để đến địa điểm thứ ba.</t>
+          <t>Đi theo ta nhé, {Male=Mr.;Female=Ms.} {PlayerName}—chúng ta cần một chiếc Gondola để đến địa điểm thứ ba.</t>
         </is>
       </c>
     </row>
@@ -9674,7 +9674,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Thậm chí ta còn không biết phải nói gì nữa.</t>
+          <t>Thậm chí tao còn không biết phải nói gì nữa.</t>
         </is>
       </c>
     </row>
@@ -9804,7 +9804,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>{PlayerName}… Liệu cậu có phải là Rover đã cứu Jinzhou mới đây, như &lt;i&gt;The Worldly Watch&lt;/i&gt; đã nhắc đến?</t>
+          <t>{PlayerName}… Liệu cậu có phải là Vận Mệnh Giả đã cứu Jinzhou mới đây, như &lt;i&gt;The Worldly Watch&lt;/i&gt; đã nhắc đến?</t>
         </is>
       </c>
     </row>
@@ -11299,7 +11299,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>{Male=cậu;Female=cô} {PlayerName} còn câu hỏi nào khác không?</t>
+          <t>bạn {PlayerName} còn câu hỏi nào khác không?</t>
         </is>
       </c>
     </row>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>{Male=Anh;Female=Chị} {PlayerName}, có gì đó không ổn... {Male=Anh;Female=Chị} có cảm giác thế không?</t>
+          <t>{Male=Mr.;Female=Ms.} {PlayerName}, có gì đó không ổn... bạn có cảm giác thế không?</t>
         </is>
       </c>
     </row>
@@ -11559,7 +11559,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Ta nghĩ nó thiếu đi cái hồn của con người.</t>
+          <t>Tao nghĩ nó thiếu đi cái hồn của con người.</t>
         </is>
       </c>
     </row>
@@ -12079,7 +12079,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>{Male=Anh;Female=Chị} {PlayerName}, đi xem thử nào!</t>
+          <t>{Male=Mr.;Female=Ms.} {PlayerName}, đi xem thử nào!</t>
         </is>
       </c>
     </row>
@@ -12339,7 +12339,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>Ta cứ nghĩ cậu luôn muốn đến Kho Lưu Trữ Cấm Chính rồi?</t>
+          <t>Tao cứ nghĩ cậu luôn muốn đến Kho Lưu Trữ Cấm Chính rồi?</t>
         </is>
       </c>
     </row>
@@ -12664,7 +12664,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Để tôi lo.</t>
+          <t>Để đó cho ta.</t>
         </is>
       </c>
     </row>
@@ -12729,7 +12729,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Ta lấy hết kho báu ở đây, biết chưa.</t>
+          <t>Tao lấy hết kho báu ở đây, biết chưa.</t>
         </is>
       </c>
     </row>
@@ -13704,7 +13704,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Tôi không hiểu, thưa {Male=ngài;Female=bà}... Chẳng phải {Male=ngài;Female=bà} được Sentinel cử đến để cứu tôi sao?</t>
+          <t>Tôi không hiểu, thưa {Male=sir;Female=lady}... Chẳng phải {Male=ngài;Female=bà} được Sentinel cử đến để cứu tôi sao?</t>
         </is>
       </c>
     </row>
@@ -14679,7 +14679,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Đợi đã. Nếu ta bảo ta có thể giúp thì sao?</t>
+          <t>Đợi đã. Nếu tao bảo tao có thể giúp thì sao?</t>
         </is>
       </c>
     </row>
@@ -15589,7 +15589,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>À, nhưng khoan đã... Ta nói hơi nhanh quá. Xin lỗi, {Male=anh;Female=chị} {PlayerName}, ta đi thôi!</t>
+          <t>À, nhưng khoan đã... Ta nói hơi nhanh quá. Xin lỗi, {Male=Mr.;Female=Ms.} {PlayerName}, ta đi thôi!</t>
         </is>
       </c>
     </row>
@@ -15719,7 +15719,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Nguyện xin Người Canh Gác ban phước lành cho {Male=anh;Female=chị} {PlayerName}!</t>
+          <t>Nguyện xin Người Canh Gác ban phước lành cho {Male=Mr.;Female=Ms.} {PlayerName}!</t>
         </is>
       </c>
     </row>
@@ -16304,7 +16304,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>{Male=Anh;Female=Chị} {PlayerName}, {Male=anh;Female=chị} đã về! {Male=Anh;Female=Chị} không sao chứ?</t>
+          <t>{Male=Mr.;Female=Ms.} {PlayerName}, bạn đã về! bạn không sao chứ?</t>
         </is>
       </c>
     </row>
@@ -16954,7 +16954,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>{Male=Anh;Female=Chị} {PlayerName}… cậu có nghĩ ta đã đi sai con đường của tổ tiên không?</t>
+          <t>{Male=Mr.;Female=Ms.} {PlayerName}… cậu có nghĩ ta đã đi sai con đường của tổ tiên không?</t>
         </is>
       </c>
     </row>
@@ -17084,7 +17084,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>Xin lỗi, {Male=anh;Female=chị} {PlayerName}. Tớ không hiểu.</t>
+          <t>Xin lỗi, {Male=Mr.;Female=Ms.} {PlayerName}. Tớ không hiểu.</t>
         </is>
       </c>
     </row>
@@ -17279,7 +17279,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>{Male=Anh;Female=Chị} {PlayerName}, đây là vu khống nghiêm trọng đối với Hội Thánh! Theo Giáo Lý Của Vực Sâu...</t>
+          <t>{Male=Mr.;Female=Ms.} {PlayerName}, đây là vu khống nghiêm trọng đối với Hội Thánh! Theo Giáo Lý Của Vực Sâu...</t>
         </is>
       </c>
     </row>
@@ -17409,7 +17409,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>{Male=Anh;Female=Chị} {PlayerName}, sao {Male=anh;Female=chị} lại nói về Hội Thánh như thể họ là kẻ ác?</t>
+          <t>{Male=Mr.;Female=Ms.} {PlayerName}, sao bạn lại nói về Hội Thánh như thể họ là kẻ ác?</t>
         </is>
       </c>
     </row>
@@ -17669,7 +17669,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>{Male=Anh;Female=Chị} {PlayerName}, dù Dàn Hợp Xướng Nimbus có phải dị giáo hay không cũng không quan trọng. Đó không phải là bản nhạc tôi muốn chơi tại Carnevale.</t>
+          <t>{Male=Mr.;Female=Ms.} {PlayerName}, dù Dàn Hợp Xướng Nimbus có phải dị giáo hay không cũng không quan trọng. Đó không phải là bản nhạc tôi muốn chơi tại Carnevale.</t>
         </is>
       </c>
     </row>
@@ -17864,7 +17864,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Ta còn chẳng biết phải bắt đầu từ đâu.</t>
+          <t>Tao còn chẳng biết phải bắt đầu từ đâu.</t>
         </is>
       </c>
     </row>
@@ -18124,7 +18124,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>{Male=Anh;Female=Chị} {PlayerName}, tại sao...</t>
+          <t>{Male=Mr.;Female=Ms.} {PlayerName}, tại sao...</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>{Male=Anh;Female=Chị} {PlayerName}, tôi nên làm gì đây? Có nên báo cáo bản nhạc này là dị giáo với Hội Thánh không? Tại sao tôi lại chần chừ? Phải chăng đức tin của tôi đang lung lay?</t>
+          <t>{Male=Mr.;Female=Ms.} {PlayerName}, tôi nên làm gì đây? Có nên báo cáo bản nhạc này là dị giáo với Hội Thánh không? Tại sao tôi lại chần chừ? Phải chăng đức tin của tôi đang lung lay?</t>
         </is>
       </c>
     </row>
@@ -18839,7 +18839,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>{Male=Anh;Female=Chị} {PlayerName}! Thật bất ngờ khi gặp lại cậu sớm thế!</t>
+          <t>{Male=Mr.;Female=Ms.} {PlayerName}! Thật bất ngờ khi gặp lại cậu sớm thế!</t>
         </is>
       </c>
     </row>
@@ -19034,7 +19034,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>{Male=Thưa anh;Female=Thưa chị} {PlayerName}, tôi phải xin lỗi {Male=anh;Female=chị} vì cách cư xử của tôi hôm đó... Tôi đã quá cố chấp.</t>
+          <t>{Male=Mr.;Female=Ms.} {PlayerName}, tôi phải xin lỗi bạn vì cách cư xử của tôi hôm đó... Tôi đã quá cố chấp.</t>
         </is>
       </c>
     </row>
@@ -19359,7 +19359,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Tất nhiên là... À hừm! {Male=Thưa anh;Female=Thưa chị} {PlayerName}, chúng ta giữ bí mật này chỉ giữa hai ta thôi nhé!</t>
+          <t>Tất nhiên là... À hừm! {Male=Mr.;Female=Ms.} {PlayerName}, chúng ta giữ bí mật này chỉ giữa hai ta thôi nhé!</t>
         </is>
       </c>
     </row>
@@ -19619,7 +19619,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>{Male=Anh;Female=Chị} {PlayerName}, {Male=anh;Female=chị} có ý kiến gì không?</t>
+          <t>{Male=Mr.;Female=Ms.} {PlayerName}, bạn có ý kiến gì không?</t>
         </is>
       </c>
     </row>
@@ -20204,7 +20204,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Đó là một nốt nhạc của Dàn hợp xướng sao? {Male=Thưa ngài;Female=Thưa cô} {PlayerName}, chúng ta hãy đi theo nó!</t>
+          <t>Đó là một nốt nhạc của Dàn hợp xướng sao? {Male=Mr.;Female=Ms.} {PlayerName}, chúng ta hãy đi theo nó!</t>
         </is>
       </c>
     </row>
@@ -20399,7 +20399,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>{Male=Anh;Female=Chị} {PlayerName}, phù… Đi trước đi! Tôi sẽ đuổi kịp ngay thôi!</t>
+          <t>{Male=Mr.;Female=Ms.} {PlayerName}, phù… Đi trước đi! Tôi sẽ đuổi kịp ngay thôi!</t>
         </is>
       </c>
     </row>
@@ -21049,7 +21049,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>{Male=Anh;Female=Chị} {PlayerName} quay lại nhanh thế! Thật đáng nể!</t>
+          <t>{Male=Mr.;Female=Ms.} {PlayerName} quay lại nhanh thế! Thật đáng nể!</t>
         </is>
       </c>
     </row>
@@ -21114,7 +21114,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>Dễ hơn ta tưởng nhiều.</t>
+          <t>Dễ hơn tao tưởng nhiều.</t>
         </is>
       </c>
     </row>
@@ -21569,7 +21569,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Ta không nghĩ nó có gì đặc biệt cả.</t>
+          <t>Tao không nghĩ nó có gì đặc biệt cả.</t>
         </is>
       </c>
     </row>
@@ -21699,7 +21699,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Hừm... Có lẽ vì {Male=anh;Female=chị} {PlayerName} không phải người bản địa của Rinascita.</t>
+          <t>Hừm... Có lẽ vì {Male=Mr.;Female=Ms.} {PlayerName} không phải người bản địa của Rinascita.</t>
         </is>
       </c>
     </row>
@@ -22089,7 +22089,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>{Male=Thưa anh;Female=Thưa chị} {PlayerName}, xin hãy giữ kín chuyện này, đừng nói với ai khác!</t>
+          <t>{Male=Mr.;Female=Ms.} {PlayerName}, xin hãy giữ kín chuyện này, đừng nói với ai khác!</t>
         </is>
       </c>
     </row>
@@ -22414,7 +22414,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>Không ai muốn một Đợt Thủy Triều Đen nữa đâu, {Male=ông;Female=bà} {PlayerName}.</t>
+          <t>Không ai muốn một Đợt Thủy Triều Đen nữa đâu, {Male=Mr.;Female=Ms.} {PlayerName}.</t>
         </is>
       </c>
     </row>
@@ -23324,7 +23324,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Phù! {Male=Anh;Female=Chị} {PlayerName}, mình lo chết đi được. Mọi chuyện ổn cả chứ?</t>
+          <t>Phù! {Male=Mr.;Female=Ms.} {PlayerName}, mình lo chết đi được. Mọi chuyện ổn cả chứ?</t>
         </is>
       </c>
     </row>
@@ -23584,7 +23584,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Ra vậy... {Male=Thưa ngài;Female=Thưa cô} {PlayerName}, thật lòng mà nói, trong lúc hồi hộp, ta đã quên cầu nguyện cho cậu. Nhưng thật may là cậu vẫn bình an!</t>
+          <t>Ra vậy... {Male=Mr.;Female=Ms.} {PlayerName}, thật lòng mà nói, trong lúc hồi hộp, ta đã quên cầu nguyện cho cậu. Nhưng thật may là cậu vẫn bình an!</t>
         </is>
       </c>
     </row>
@@ -25014,7 +25014,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Giờ thì cậu làm ta đói mất rồi.</t>
+          <t>Giờ thì cậu làm tao đói mất rồi.</t>
         </is>
       </c>
     </row>
@@ -27354,7 +27354,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Ừm, ta cũng nghĩ là mình đã gặp hắn trước đây rồi.</t>
+          <t>Ừm, tao cũng nghĩ là mình đã gặp hắn trước đây rồi.</t>
         </is>
       </c>
     </row>
@@ -28719,7 +28719,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Ừm, ta cũng nghĩ là mình đã gặp hắn trước đây rồi.</t>
+          <t>Ừm, tao cũng nghĩ là mình đã gặp hắn trước đây rồi.</t>
         </is>
       </c>
     </row>
@@ -29564,7 +29564,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Phù, thật may cậu đã ở đây. Đối phó với mấy con Tacet Discord một mình vẫn hơi quá sức với ta.</t>
+          <t>Phù, thật may cậu đã ở đây. Đối phó với mấy con Tacet Discord một mình vẫn hơi quá sức với tao.</t>
         </is>
       </c>
     </row>
@@ -30149,7 +30149,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>Ta cứ tưởng cậu cần ta giúp mà.</t>
+          <t>Tao cứ tưởng cậu cần tao giúp mà.</t>
         </is>
       </c>
     </row>
@@ -30799,7 +30799,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Cứ gọi ta là {PlayerName} thôi. Ta chỉ tình cờ đi ngang qua và làm những gì có thể.</t>
+          <t>Cứ gọi tao là {PlayerName} thôi. Tao chỉ tình cờ đi ngang qua và làm những gì có thể.</t>
         </is>
       </c>
     </row>
@@ -31384,7 +31384,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Chà, câu chuyện dài lắm. Hồi nhỏ, ta lạc trong hoang dã và gặp mấy con Tacet Discord đáng sợ vào ban đêm. Đang nghĩ mình xong đời rồi thì có người xuất hiện, cầm kiếm và cứu ta.</t>
+          <t>Chà, câu chuyện dài lắm. Hồi nhỏ, tao lạc trong hoang dã và gặp mấy con Tacet Discord đáng sợ vào ban đêm. Đang nghĩ mình xong đời rồi thì có người xuất hiện, cầm kiếm và cứu tao.</t>
         </is>
       </c>
     </row>
@@ -31644,7 +31644,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Tớ biết. Có thể khó nhận ra, nhưng tớ cũng là một Cộng Hưởng Giả.</t>
+          <t>Tớ biết. Có thể khó nhận ra, nhưng tớ cũng là một Resonator.</t>
         </is>
       </c>
     </row>
@@ -32554,7 +32554,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Chỉ cần đừng có nhắc tên ta mỗi khi ngươi làm hỏng việc là được!</t>
+          <t>Chỉ cần đừng có nhắc tên tao mỗi khi mày làm hỏng việc là được!</t>
         </is>
       </c>
     </row>
@@ -32684,7 +32684,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Ta hứa, ta sẽ không làm cậu thất vọng đâu.</t>
+          <t>Tao hứa, tao sẽ không làm cậu thất vọng đâu.</t>
         </is>
       </c>
     </row>
